--- a/views/produtos.xlsx
+++ b/views/produtos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="D2" t="n">
         <v>0.85</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2601</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>salg. keus bacon</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
